--- a/storage/app/DATA_SECURE.xlsx
+++ b/storage/app/DATA_SECURE.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,85 +436,5134 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HALBERG NG</t>
+          <t>AKBAR ADRIANO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>XII TKJ IND</t>
+          <t>XII AK 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PZV1CeT3kU1m</t>
+          <t>SEC-AKB-1000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MUHAMMAD RAIHAND FERSA</t>
+          <t>AISHA MAHARANI SUZANTA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>XII TKJ IND</t>
+          <t>XII AK 1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bXzsvFPy9W72</t>
+          <t>SEC-AIS-1001</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MUHAMMAD AIDIL FITRAH</t>
+          <t>ALIN NUR AZIFA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XII TKJ IND</t>
+          <t>XII AK 1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pRTebAaKbmk8</t>
+          <t>SEC-ALI-1002</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MUHAMMAD ZULFIKAR UDHRI</t>
+          <t>ALZA NUR ULFIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XII TKJ IND</t>
+          <t>XII AK 1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dE5oCU2wZcmv</t>
+          <t>SEC-ALZ-1003</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>ANGELA TAY</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SEC-ANG-1004</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ASRIL MAULANA SAPUTRA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SEC-ASR-1005</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CANDY</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SEC-CAN-1006</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CINTIA SETIOWATI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SEC-CIN-1007</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DELLA NOVITA SARI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SEC-DEL-1008</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DETHIA TIMUR</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SEC-DET-1009</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DINI RAHMADANI</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SEC-DIN-1010</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ERVIN</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SEC-ERV-1011</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HAIRUN NISA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SEC-HAI-1012</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>JAEVIN KENANDO</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SEC-JAE-1013</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>JENYFER ARDHIDA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SEC-JEN-1014</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>JESSICA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SEC-JES-1015</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>JOICE CECILYA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SEC-JOI-1016</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>JULIUS EMILIO TAN</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SEC-JUL-1017</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LILI JULITA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SEC-LIL-1018</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MAYANG SARI</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SEC-MAY-1019</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MERIANTI</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SEC-MER-1020</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MIRA AULIA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SEC-MIR-1021</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MUHAMMAD BAGUS PRASETYO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SEC-MUH-1022</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NAYLA ALVENITA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SEC-NAY-1023</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NOER HAYATI</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SEC-NOE-1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>OKTAVIANI DESMIANSYAH</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SEC-OKT-1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>RIAN ERDIANTO</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SEC-RIA-1026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SALSABILA SABHAS</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SEC-SAL-1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SELLY SAFARI</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SEC-SEL-1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SELVIYANAWATI</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SEC-SEL-1029</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SITI NURIMAH</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SEC-SIT-1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SYAHRANI RAFIFA RAMADHANI</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SEC-SYA-1031</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TESYA AMELIA PUTRI</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SEC-TES-1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TRIAN NOVAL RIVANZA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SEC-TRI-1033</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>YUNI</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SEC-YUN-1034</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ZELFA FARIANTINA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>XII AK 1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SEC-ZEL-1035</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AL HAKIM</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SEC-AL -1036</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ALLIYA MARETHA WULANSARI</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SEC-ALL-1037</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ANGLE JULYANA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SEC-ANG-1038</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ARDI SAPUTRA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SEC-ARD-1039</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AULIA MARTA ANGGRAINI</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SEC-AUL-1040</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BELLA YUDISTIARA PUTRI</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SEC-BEL-1041</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CAROLINE JESSICA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SEC-CAR-1042</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>DELLA RAHMAWATI</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SEC-DEL-1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>E L L A</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SEC-E L-1044</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ELLISA TAN</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SEC-ELL-1045</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>EVELYN RICADONA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SEC-EVE-1046</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>FADHLAN ALFARIS</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SEC-FAD-1047</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>JESSICA</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SEC-JES-1048</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>JESTINE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SEC-JES-1049</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>JULIANA SUGIANA</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SEC-JUL-1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MARSHA SAHARA</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SEC-MAR-1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MUHAMMAD IQBAL APRILIAN</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SEC-MUH-1052</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MUHAMMAD NABIL ROHMAN</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SEC-MUH-1053</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>NURLINDA FEBRIYANA</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SEC-NUR-1054</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PUTRI YANASARI</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SEC-PUT-1055</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>RIDWANSAH</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SEC-RID-1056</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SHALVYNE TAN</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SEC-SHA-1057</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SHERLY LU</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SEC-SHE-1058</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>STEFHANY</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SEC-STE-1059</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>TEDI IRWANSYAH</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SEC-TED-1060</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>VEBRA VALENTINO</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>XII AK 2</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SEC-VEB-1061</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>CALVINA CANDRIANI</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>XII AK 3</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SEC-CAL-1062</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ELISYA SEPTINA</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>XII AK 3</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SEC-ELI-1063</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ELLIS MARCIA</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>XII AK 3</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>SEC-ELL-1064</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>LILIA ANTANIA</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>XII AK 3</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SEC-LIL-1065</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>JENIFFER</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>XII AK 3</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SEC-JEN-1066</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>JULIANTO</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>XII AK 3</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SEC-JUL-1067</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>VIONA ANGELIN</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>XII AK 3</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SEC-VIO-1068</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>VIVIAN GO</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>XII AK 3</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SEC-VIV-1069</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ANNISA DWI PUTRI</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>XII LPS</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SEC-ANN-1070</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ARUMY AINUN MARDIAH</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>XII LPS</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SEC-ARU-1071</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>CANTIKA APRILIA</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>XII LPS</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SEC-CAN-1072</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>E. VICKY ANUGERAH RAMADHAN</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>XII LPS</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SEC-E. -1073</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>FIKA RAHMAWATI ARMAINSA</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>XII LPS</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SEC-FIK-1074</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>FRIZHA MUTTHIA ISKANDAR</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>XII LPS</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SEC-FRI-1075</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>IIS SATRIYANI</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>XII LPS</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SEC-IIS-1076</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>JENEYSAH MUTIA ARMAYANTI</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>XII LPS</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SEC-JEN-1077</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>LAURA VALENSIA</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>XII LPS</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>SEC-LAU-1078</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MARDIANTI</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>XII LPS</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SEC-MAR-1079</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MAYA ANGGI SAVITRI</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>XII LPS</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SEC-MAY-1080</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>MELIA PUTRI</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>XII LPS</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SEC-MEL-1081</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MUHAMMAD ZHAFRAN</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>XII LPS</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>SEC-MUH-1082</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>NADYA SYAKIRA</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>XII LPS</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SEC-NAD-1083</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>NOVAN MARDIYANTO</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>XII LPS</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>SEC-NOV-1084</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>NUR SIFANA KOLBI</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>XII LPS</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>SEC-NUR-1085</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>QAIFA AZWINA SYAHIRA</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>XII LPS</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>SEC-QAI-1086</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>SHAFIA NANDA ALTHAFUNNISA</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>XII LPS</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SEC-SHA-1087</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>VIOLLA SONIARTA PUTRI</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>XII LPS</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SEC-VIO-1088</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ZAHRA AULYA PUTRI</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>XII LPS</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SEC-ZAH-1089</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ANGGA DWI RAHMADAN</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>XII MP 1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SEC-ANG-1090</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>BALQISH RIEZQIA FITRA</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>XII MP 1</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>SEC-BAL-1091</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>CAYLILA ORIMOZA SATIVA</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>XII MP 1</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>SEC-CAY-1092</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>DELA SILFAWATI</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>XII MP 1</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>SEC-DEL-1093</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>DESLIANY AULIA FITRI</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>XII MP 1</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>SEC-DES-1094</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>DESY NIKA PUSPITASARI</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>XII MP 1</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>SEC-DES-1095</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ENJEL DONATA</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>XII MP 1</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>SEC-ENJ-1096</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>EVA</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>XII MP 1</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>SEC-EVA-1097</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>FIRDA AZZURA</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>XII MP 1</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>SEC-FIR-1098</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>FRISKA ELVIERA SETIAWAN SARI</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>XII MP 1</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>SEC-FRI-1099</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>LADYSTA LAIRIS NASUTION</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>XII MP 1</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>SEC-LAD-1100</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>MARISA AUDINA PUTRI</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>XII MP 1</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>SEC-MAR-1101</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>MARSYA ZAKIRAH</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>XII MP 1</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>SEC-MAR-1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>MUHD. FATHIR  AL HAKIM</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>XII MP 1</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>SEC-MUH-1103</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>NADYLLA OCTAVIA</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>XII MP 1</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>SEC-NAD-1104</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>NAZWA PUTRI MULIANANDA</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>XII MP 1</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>SEC-NAZ-1105</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>OKTAVIA SUCI ANGGRAINI</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>XII MP 1</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SEC-OKT-1106</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>PUTRA MAULANSYAH</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>XII MP 1</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>SEC-PUT-1107</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>RIZKY ENDRIYANA</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>XII MP 1</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>SEC-RIZ-1108</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>RIYANTI PUTRI</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>XII MP 1</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>SEC-RIY-1109</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>SAVIRA MARIA RAMADANI</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>XII MP 1</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SEC-SAV-1110</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>SYARIFAH AZZHILA RHAMADANI</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>XII MP 1</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SEC-SYA-1111</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>ARSHYA VARIESSYA XALVADHINDA</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>XII MP 2</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>SEC-ARS-1112</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>CINDY AURORA EFFILIANCY</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>XII MP 2</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>SEC-CIN-1113</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>CINTA MELDHIASTARI</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>XII MP 2</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>SEC-CIN-1114</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>CUT OKTARI FITRIYANTI</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>XII MP 2</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>SEC-CUT-1115</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>DINA AULIA</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>XII MP 2</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>SEC-DIN-1116</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>DIVYA AZZAHRA</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>XII MP 2</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>SEC-DIV-1117</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>JUWITA AYU PUTRI</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>XII MP 2</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>SEC-JUW-1118</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>KANAYA NANDA RIVETHA</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>XII MP 2</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SEC-KAN-1119</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>KHANSAA NOVRIHAFIK</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>XII MP 2</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SEC-KHA-1120</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>LIA RIZKA MUMTAZA</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>XII MP 2</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>SEC-LIA-1121</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>MARSA YUWANDA</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>XII MP 2</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>SEC-MAR-1122</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>MUHAMMAD SYAHDIKIN</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>XII MP 2</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>SEC-MUH-1123</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>NATASYA AMANDA STEVFANI</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>XII MP 2</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>SEC-NAT-1124</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>NAYLA ZAHRA GIOVALENT</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>XII MP 2</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>SEC-NAY-1125</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>NUR ATIKA AZIVAH</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>XII MP 2</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>SEC-NUR-1126</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>NURAISHA RAMADHANI</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>XII MP 2</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>SEC-NUR-1127</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>PERMATA CAHAYANEIH FITRI</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>XII MP 2</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>SEC-PER-1128</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>RAI SYAH RAMAHDANI</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>XII MP 2</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>SEC-RAI-1129</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>RISKA INDAH LESTARI</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>XII MP 2</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>SEC-RIS-1130</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>SELVANI MELIANZA</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>XII MP 2</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>SEC-SEL-1131</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>SRI NUR AISYAH</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>XII MP 2</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>SEC-SRI-1132</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>VERA DWI ARUYATI</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>XII MP 2</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>SEC-VER-1133</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>VICI MELVIANA SETIAWAN</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>XII MP 2</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>SEC-VIC-1134</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>WAN REGITA VAZHA NURUL DZIHNI</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>XII MP 2</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>SEC-WAN-1135</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ARZITA SYERWINA</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>SEC-ARZ-1136</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ASY SYIFAA NOVIANDARA</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>SEC-ASY-1137</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>CARIEN AMMABEL</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>SEC-CAR-1138</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>CINTA MUSTIKA SARI</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>SEC-CIN-1139</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>DESTA AULIA</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>SEC-DES-1140</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>DIVA RENATA</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>SEC-DIV-1141</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>FERDIAN BAGUS SAHPUTRA</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>SEC-FER-1142</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>INDAH SRI MULYANI</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>SEC-IND-1143</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>INTAN HARAHAP</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>SEC-INT-1144</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>IZHNI FABILLA</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>SEC-IZH-1145</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>JENNYFER LOPEZ PHILIP</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>SEC-JEN-1146</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>JUWITA SUNARDI</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>SEC-JUW-1147</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>KHARISYA TANTYA PUTRI</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>SEC-KHA-1148</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>M. FAREL ADIWIJAYA</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>SEC-M. -1149</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>MEYLISA PUTRI DRIANI</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>SEC-MEY-1150</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>MUHAMMAD HAMIZUL PIRDIYANSYAH</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>SEC-MUH-1151</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>NURHAIRUNNISA</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>SEC-NUR-1152</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>OLIVIA</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>SEC-OLI-1153</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>PUTRI KHUSNUL KHOTIMAH</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>SEC-PUT-1154</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>REFRAN DIAS ANANTO</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>SEC-REF-1155</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>REVA SASALBILLA</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>SEC-REV-1156</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>RICA ANJELINE LOIS EUNIKE SIBUEA</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>SEC-RIC-1157</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>SABRINA BILQIS FEBRIANI</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>SEC-SAB-1158</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>THERESA GANIS RAHMANIA</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>SEC-THE-1159</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>ZERFIKAR SYAPUTRA</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>XII MP 3</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>SEC-ZER-1160</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>WINRIA LIUS</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>XII BR 1</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>SEC-WIN-1161</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>AHMAT DAUT</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>XII BR 2</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>SEC-AHM-1162</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>ALBER RIZKY SABIAN</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>XII BR 2</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>SEC-ALB-1163</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>ALIF</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>XII BR 2</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>SEC-ALI-1164</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>CELSI</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>XII BR 2</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>SEC-CEL-1165</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>DIMAS PANDU ASMARA PUTRA</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>XII BR 2</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>SEC-DIM-1166</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>KELVIN</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>XII BR 2</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>SEC-KEL-1167</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>KIRANA CINTA LISTARI</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>XII BR 2</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>SEC-KIR-1168</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>MUHAMMAD NURDIYANSYAH</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>XII BR 2</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>SEC-MUH-1169</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>NADIRA SELVIA</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>XII BR 2</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>SEC-NAD-1170</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>RESTY ERLY NOVIANTY</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>XII BR 2</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>SEC-RES-1171</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>SILA MARISCA</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>XII BR 2</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>SEC-SIL-1172</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>TARA AGUSTIN</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>XII BR 2</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>SEC-TAR-1173</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>ZARINA EKA SAFITRI</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>XII BR 2</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>SEC-ZAR-1174</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>ANDERSEN FERNANDO</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>XII BD</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>SEC-AND-1175</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>ANDRY</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>XII BD</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>SEC-AND-1176</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>ANGELISA</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>XII BD</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>SEC-ANG-1177</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>CHELSEA</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>XII BD</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>SEC-CHE-1178</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>DARRICH</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>XII BD</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>SEC-DAR-1179</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>DELVIN TAN</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>XII BD</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>SEC-DEL-1180</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>DEVEN HERNANDO</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>XII BD</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>SEC-DEV-1181</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>KELVIN LIE</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>XII BD</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>SEC-KEL-1182</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>KELVIN NG</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>XII BD</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>SEC-KEL-1183</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>KRIS WILUAN</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>XII BD</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>SEC-KRI-1184</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>MEDY AULIA ANGGA LETA</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>XII BD</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>SEC-MED-1185</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>MUHAMAD REZHA PRASETYA HADI</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>XII BD</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>SEC-MUH-1186</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>NICHOLAS ONG</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>XII BD</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>SEC-NIC-1187</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>VIONA</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>XII BD</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>SEC-VIO-1188</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>YANNI</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>XII BD</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>SEC-YAN-1189</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>ANDREW JOEL PANJAITAN</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>XII DKV 1</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>SEC-AND-1190</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>ANDROS MAULANA</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>XII DKV 1</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>SEC-AND-1191</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>FATURROHMAN</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>XII DKV 1</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>SEC-FAT-1192</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>GHISYAN ANITA SARDI</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>XII DKV 1</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>SEC-GHI-1193</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>JENNY RAHMA DHANI</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>XII DKV 1</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>SEC-JEN-1194</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>KEVINDA RIAD</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>XII DKV 1</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>SEC-KEV-1195</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>KIRANA DEWI ARTIKASARI</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>XII DKV 1</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>SEC-KIR-1196</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>NAYLA PUTRI NAZWA</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>XII DKV 1</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>SEC-NAY-1197</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>OKTO RAYHAN MARTIAHADI</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>XII DKV 1</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>SEC-OKT-1198</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>PRICILLA WEE SIU TIN</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>XII DKV 1</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>SEC-PRI-1199</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>RAMADANI AULIA FITRI</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>XII DKV 1</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>SEC-RAM-1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>RINA MARLIANTI</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>XII DKV 1</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>SEC-RIN-1201</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>RISKA SAFITRI</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>XII DKV 1</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>SEC-RIS-1202</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>SAFIRA SALWA</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>XII DKV 1</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>SEC-SAF-1203</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>WAHYUNI SUCI RAHMAT DANI</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>XII DKV 1</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>SEC-WAH-1204</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>WELRENCE ENSTAINE</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>XII DKV 1</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>SEC-WEL-1205</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>YELLO SEPTY RAHMADAN</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>XII DKV 1</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>SEC-YEL-1206</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>ALUNA DIVA AZZAHRA</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>SEC-ALU-1207</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>ANDRE YOGI SAPUTRA</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>SEC-AND-1208</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>AULIA APRIANDA PUTRI</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>SEC-AUL-1209</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>AULIA RAMADHANI FITRI</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>SEC-AUL-1210</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>BRYAN SERDYCO</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>SEC-BRY-1211</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>CHARLES</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>SEC-CHA-1212</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>DEDY PRASETIYA RAMADAN</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>SEC-DED-1213</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>DENNIS ANDERSENZ</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>SEC-DEN-1214</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>ELAINE</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>SEC-ELA-1215</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>FEBRI DWI HARYANI</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>SEC-FEB-1216</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>FREDRICK NG</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>SEC-FRE-1217</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>GILANG ADHI WIJAYA</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>SEC-GIL-1218</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>HENRY ALEXIS ZHANG</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>SEC-HEN-1219</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>JACKSON ALVINO</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>SEC-JAC-1220</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>JENNY TRYESA</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>SEC-JEN-1221</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>JESICCA</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>SEC-JES-1222</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>MELVIN HERMANSON</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>SEC-MEL-1223</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>MICHAEL WIJAYA</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>SEC-MIC-1224</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>MUHAMMAD DHEVAN ARIF NUGRAHA</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>SEC-MUH-1225</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>MUHAMMAD RIZKY FAIRUZ</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>SEC-MUH-1226</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>NUR DELZA HAIFA</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>SEC-NUR-1227</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>ORIZA SATIVA</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>SEC-ORI-1228</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>RISDA HIDAYAH</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>SEC-RIS-1229</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>THOMES ONG</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>SEC-THO-1230</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>WILAN</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>SEC-WIL-1231</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>WILDAN ZAINAL KHAFID</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>XII DKV 2</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>SEC-WIL-1232</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>ALPINO BINTANA</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>XII TKJ 1</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>SEC-ALP-1233</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>DIMAS RIZKI MAULANA</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>XII TKJ 1</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>SEC-DIM-1234</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>HARI AIDIL</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>XII TKJ 1</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>SEC-HAR-1235</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>INDAH ANJANI PONGSITAMMU</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>XII TKJ 1</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>SEC-IND-1236</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>M. RIDWAN</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>XII TKJ 1</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>SEC-M. -1237</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>MUHAMMAD DWIKY IRAWAN</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>XII TKJ 1</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>SEC-MUH-1238</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>MUHAMMAD FADEL</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>XII TKJ 1</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>SEC-MUH-1239</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>MUHAMMAD FATHIR</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>XII TKJ 1</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>SEC-MUH-1240</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>PRAMUDITA DWI NURZAKY SAPUTRA</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>XII TKJ 1</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>SEC-PRA-1241</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>REFAN HAIKAL MAULANA</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>XII TKJ 1</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>SEC-REF-1242</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>RENDI SAPUTRA</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>XII TKJ 1</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>SEC-REN-1243</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>SHANANG BAGUS PRIMAYUDHA</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>XII TKJ 1</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>SEC-SHA-1244</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>ANDRY IRWANSYAH</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>XII TKJ 2</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>SEC-AND-1245</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>HEIDY ATA</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>XII TKJ 2</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>SEC-HEI-1246</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>MUHAMMAD ALFIN SAPUTRA</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>XII TKJ 2</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>SEC-MUH-1247</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>MUHAMMAD REYHAN ARRIZKY</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>XII TKJ 2</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>SEC-MUH-1248</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>NAFIQ SYAIFULLOH</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>XII TKJ 2</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>SEC-NAF-1249</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>PUTRI APRILLIANA LUBIS</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>XII TKJ 2</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>SEC-PUT-1250</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>RAFFY AZALDI</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>XII TKJ 2</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>SEC-RAF-1251</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>RAIHAN MUSTAQIM</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>XII TKJ 2</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>SEC-RAI-1252</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>SILVA AZZAHRA PUTRI</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>XII TKJ 2</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>SEC-SIL-1253</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>HALBERG NG</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>XII TKJ IND</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>SEC-HAL-1254</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>MUHAMMAD RAIHAND FERSA</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>XII TKJ IND</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>SEC-MUH-1255</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>MUHAMMAD AIDIL FITRAH</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>XII TKJ IND</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>SEC-MUH-1256</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>MUHAMMAD ZULFIKAR UDHRI</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>XII TKJ IND</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>SEC-MUH-1257</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
           <t>ZEANDRA ALFARENZA</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B260" t="inlineStr">
         <is>
           <t>XII TKJ IND</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DdAunIkQC3DJ</t>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>SEC-ZEA-1258</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>AGIL RAMADANA</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>XII TJAT</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>SEC-AGI-1259</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>APRIANDI ZIKRI PRATAMA</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>XII TJAT</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>SEC-APR-1260</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>ARIF BUDIMAN JEHADU</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>XII TJAT</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>SEC-ARI-1261</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>CHELSEA</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>XII TJAT</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>SEC-CHE-1262</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>DEFRANT LUCHAS RAFA SIDAURUK</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>XII TJAT</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>SEC-DEF-1263</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>DICKY ASSADAD</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>XII TJAT</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>SEC-DIC-1264</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>DIMAS FAJRI DANISYAH</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>XII TJAT</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>SEC-DIM-1265</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>DINDA FEBBIANTY</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>XII TJAT</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>SEC-DIN-1266</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>FAHRIANSYAH DISRA DAVA</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>XII TJAT</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>SEC-FAH-1267</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>FAREL AIDIL PRATAMA</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>XII TJAT</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>SEC-FAR-1268</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>FARHAN HAKIM</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>XII TJAT</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>SEC-FAR-1269</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>FITRA OKTAVIAN</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>XII TJAT</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>SEC-FIT-1270</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>GHATHFAN ALI</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>XII TJAT</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>SEC-GHA-1271</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>HAIKAL FATAHN RIDLA</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>XII TJAT</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>SEC-HAI-1272</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>JOVAN ANADITO</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>XII TJAT</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>SEC-JOV-1273</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>LOUIS AGUNG FEBRIANTO</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>XII TJAT</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>SEC-LOU-1274</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>M.IHSAN MUBARAK</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>XII TJAT</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>SEC-M.I-1275</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>MUHAMMAD ILHAM ROMADHANA</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>XII TJAT</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>SEC-MUH-1276</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>MUHAMMAD YUGA SYAPUTRA</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>XII TJAT</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>SEC-MUH-1277</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>NOVA SAPUTRA PERMAIDANI WIYONO</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>XII TJAT</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>SEC-NOV-1278</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>RAHMAN NURSYAQBAN</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>XII TJAT</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>SEC-RAH-1279</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>RHANKY ALIF ZAFFANI</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>XII TJAT</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>SEC-RHA-1280</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>SANTOSO</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>XII TJAT</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>SEC-SAN-1281</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>WENKY</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>XII TJAT</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>SEC-WEN-1282</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>ADHITYA ALIFZIADY</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>XII TL</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>SEC-ADH-1283</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>ADYTIA BAYU PRASETYO</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>XII TL</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>SEC-ADY-1284</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>AHMAD AZANI</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>XII TL</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>SEC-AHM-1285</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>AISYAH FUJINUGRAINI</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>XII TL</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>SEC-AIS-1286</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>BIENOKTA DEI MASAJI</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>XII TL</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>SEC-BIE-1287</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>DARMAWAN SAPUTRA</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>XII TL</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>SEC-DAR-1288</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>DEREN</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>XII TL</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>SEC-DER-1289</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>DIEMAS ADJI PRATAMA</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>XII TL</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>SEC-DIE-1290</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>ELLYVIANA ALMAIDAH</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>XII TL</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>SEC-ELL-1291</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>I.BEBBY SEPTYANI</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>XII TL</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>SEC-I.B-1292</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>IRFAN ISMAIL</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>XII TL</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>SEC-IRF-1293</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>KHALIS RIVANO</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>XII TL</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>SEC-KHA-1294</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>M.ALIF INFIANSYAH</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>XII TL</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>SEC-M.A-1295</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>MUHAMMAD SANI</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>XII TL</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>SEC-MUH-1296</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>RAMADAN</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>XII TL</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>SEC-RAM-1297</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>SELAMAT NG</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>XII TL</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>SEC-SEL-1298</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>SHEFIA SUCI RAMADANI</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>XII TL</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>SEC-SHE-1299</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>TIARA KUSUMA NINGSIH</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>XII TL</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>SEC-TIA-1300</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>VIKO FADILLAH</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>XII TL</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>SEC-VIK-1301</t>
         </is>
       </c>
     </row>
